--- a/diseases/d033/1995-1999.xlsx
+++ b/diseases/d033/1995-1999.xlsx
@@ -5942,7 +5942,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27299,7 +27299,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28099,7 +28099,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28899,7 +28899,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31299,7 +31299,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -37735,7 +37735,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -39793,7 +39793,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40832,7 +40832,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41871,7 +41871,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42910,7 +42910,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -43949,7 +43949,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46027,7 +46027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -47066,7 +47066,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -49144,7 +49144,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -50183,7 +50183,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -57009,7 +57009,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -59067,7 +59067,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -61145,7 +61145,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -62184,7 +62184,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -63223,7 +63223,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -64262,7 +64262,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -65301,7 +65301,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -66340,7 +66340,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -67379,7 +67379,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -68418,7 +68418,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -69457,7 +69457,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -76283,7 +76283,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -78341,7 +78341,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -79380,7 +79380,7 @@
       </c>
       <c r="AM390" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN390" t="b">
@@ -80419,7 +80419,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -81458,7 +81458,7 @@
       </c>
       <c r="AM400" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN400" t="b">
@@ -82497,7 +82497,7 @@
       </c>
       <c r="AM405" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN405" t="b">
@@ -83536,7 +83536,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -84575,7 +84575,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -85614,7 +85614,7 @@
       </c>
       <c r="AM420" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN420" t="b">
@@ -86653,7 +86653,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -87692,7 +87692,7 @@
       </c>
       <c r="AM430" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN430" t="b">
@@ -88731,7 +88731,7 @@
       </c>
       <c r="AM435" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN435" t="b">

--- a/diseases/d033/1995-1999.xlsx
+++ b/diseases/d033/1995-1999.xlsx
@@ -5942,7 +5942,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27299,7 +27299,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28099,7 +28099,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28899,7 +28899,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31299,7 +31299,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -37735,7 +37735,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -39793,7 +39793,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40832,7 +40832,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41871,7 +41871,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42910,7 +42910,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -43949,7 +43949,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46027,7 +46027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -47066,7 +47066,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -49144,7 +49144,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -50183,7 +50183,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -57009,7 +57009,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -59067,7 +59067,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -61145,7 +61145,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -62184,7 +62184,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -63223,7 +63223,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -64262,7 +64262,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -65301,7 +65301,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -66340,7 +66340,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -67379,7 +67379,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -68418,7 +68418,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -69457,7 +69457,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -76283,7 +76283,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -78341,7 +78341,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -79380,7 +79380,7 @@
       </c>
       <c r="AM390" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN390" t="b">
@@ -80419,7 +80419,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -81458,7 +81458,7 @@
       </c>
       <c r="AM400" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN400" t="b">
@@ -82497,7 +82497,7 @@
       </c>
       <c r="AM405" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN405" t="b">
@@ -83536,7 +83536,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -84575,7 +84575,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -85614,7 +85614,7 @@
       </c>
       <c r="AM420" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN420" t="b">
@@ -86653,7 +86653,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -87692,7 +87692,7 @@
       </c>
       <c r="AM430" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN430" t="b">
@@ -88731,7 +88731,7 @@
       </c>
       <c r="AM435" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN435" t="b">
